--- a/p6_deployment/data/england/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/england/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,86 +434,814 @@
           <t>copiado_avoid_nan</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>jXP8f29S</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>Kl1AOZN9</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">donohue m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>htCzjMHq</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>t4kJMDhM</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>z51uktXk</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>CntkHiGq</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>nu5ql0nd</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>hdlcFVpd</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0rgRCqPd</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>pjyqwZx3</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brooks j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vZiVB3v3</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>tIUiyD7F</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dAnzBNg9</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>nHdPI4il</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bond d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>z1ovAs9F</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>8WpYGrM0</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bond d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Sd97hFwr</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>tYjCfe2E</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>t0DBiZhl</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>OMDVg8x9</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>UwJevjpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>jXcAnQUr</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>fRe0c20b</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kitchen a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>CnnJp4ae</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>bw1zAKS6</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>C2sV0kf7</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>x6klsVh3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>b3pRrrU7</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>WfkfPdXH</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SMr3Nz2U</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>xYBLuIHb</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">langford o 
+  eng </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>OS3AwgCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>6os5wmhS</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Kl7vhn7L</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>nw6fJO5K</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>bHPacsq1</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>MwmHgKaN</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>lQl9etVA</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>KWD8eLDD</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xUXzYQFk</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>CCV9JR0d</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>bsinRI25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>GbaVU03t</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eltringham g 
+  eng </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>tOTmlbNp</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>nPQL4PjR</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>pWhdu9NF</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>6NnRD2Ts</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>tMUvLt7h</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>WSQqW4p2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>vaX1LmWq</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>vyoZBtbf</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>8tPSZqtA</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>8tPSZqtA</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>697ha3El</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bell j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/england/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/england/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,7 +661,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>fmqtFMjD</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -675,7 +675,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -687,7 +687,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>AeRSxQrK</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -695,32 +695,51 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrott s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t xml:space="preserve">madley a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UwJevjpg</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+          <t>tYjCfe2E</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -728,21 +747,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">kitchen a 
+          <t xml:space="preserve">barrott s 
   eng </t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>fcpIzd9s</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -753,44 +772,40 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+          <t>fRe0c20b</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kitchen a 
+  eng </t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">smith j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>C2sV0kf7</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>U3POrPvM</t>
-        </is>
-      </c>
+          <t>CnnJp4ae</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -801,57 +816,55 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>C2sV0kf7</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">smith j 
-  eng </t>
-        </is>
-      </c>
+          <t>x6klsVh3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>U3POrPvM</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
+          <t>b3pRrrU7</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -859,43 +872,60 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">langford o 
+          <t xml:space="preserve">smith j 
   eng </t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OS3AwgCU</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>SMr3Nz2U</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
+          <t>xYBLuIHb</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">langford o 
+  eng </t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>OS3AwgCU</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -906,29 +936,18 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinson t 
-  eng </t>
-        </is>
-      </c>
+          <t>Kl7vhn7L</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -939,24 +958,29 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -967,35 +991,35 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
+          <t>lQl9etVA</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
+          <t>KWD8eLDD</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>AHNtWa3o</t>
-        </is>
-      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1006,111 +1030,111 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eltringham g 
-  eng </t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>MsDWbjnD</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ward g 
-  eng </t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Y39YvFx6</t>
-        </is>
-      </c>
+          <t>bsinRI25</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eltringham g 
+  eng </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+          <t>tOTmlbNp</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>nPQL4PjR</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
+          <t>pWhdu9NF</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>tMUvLt7h</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1121,35 +1145,35 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>2FcwTvYh</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>tMUvLt7h</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
+          <t>EBSD6oME</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>phM8NElP</t>
-        </is>
-      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1160,7 +1184,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>vyoZBtbf</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1169,7 +1193,7 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EoQjC3VB</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1177,33 +1201,18 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ward g 
-  eng </t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>8tPSZqtA</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Y39YvFx6</t>
-        </is>
-      </c>
+          <t>n1hhaOVo</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
+          <t>vyoZBtbf</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1212,7 +1221,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8tPSZqtA</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1220,24 +1229,67 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>8tPSZqtA</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>pbFTwdnB</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>8tPSZqtA</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
           <t>697ha3El</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" t="inlineStr">
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
         <is>
           <t xml:space="preserve">bell j 
   eng </t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>AHNtWa3o</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>n94TZqsm</t>
         </is>
